--- a/jpcore-r4/main/StructureDefinition-jp-medicationratio-doseperperiod.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationratio-doseperperiod.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="182">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>
@@ -266,7 +266,7 @@
 </t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 rat-1:分子と分母の両方が存在するか、両方が存在します。両方が欠席している場合、いくつかの拡張が存在するものとします / Numerator and denominator SHALL both be present, or both are absent. If both are absent, there SHALL be some extension present {(numerator.empty() xor denominator.exists()) and (numerator.exists() or extension.exists())}</t>
   </si>
   <si>
@@ -331,11 +331,14 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Ratio.numerator</t>
+  </si>
+  <si>
+    <t>Y</t>
   </si>
   <si>
     <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationQuantity}
@@ -345,17 +348,11 @@
     <t>投与量</t>
   </si>
   <si>
-    <t>薬剤に関する数量と単位を定めている。ValueおよびCodeを必須としている。単位についてはMERIT9医薬品単位略号の利用を推進している。(**SHOULD**)</t>
-  </si>
-  <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-qty-3:ユニットのコードが存在する場合、システムも存在するものとします / If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}</t>
-  </si>
-  <si>
-    <t>SN (see also Range) or CQ</t>
-  </si>
-  <si>
-    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
+    <t>.numerator</t>
   </si>
   <si>
     <t>Ratio.numerator.id</t>
@@ -365,9 +362,6 @@
   </si>
   <si>
     <t>Ratio.numerator.value</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <t xml:space="preserve">decimal
@@ -381,10 +375,6 @@
   </si>
   <si>
     <t>Quantity.value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
   </si>
   <si>
     <t>SN.2  / CQ - N/A</t>
@@ -1392,20 +1382,18 @@
         <v>76</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N5" t="s" s="2">
         <v>107</v>
       </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>76</v>
@@ -1463,24 +1451,24 @@
         <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>108</v>
       </c>
       <c r="AK5" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL5" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="AL5" t="s" s="2">
-        <v>110</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1583,10 +1571,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1691,10 +1679,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1714,22 +1702,22 @@
         <v>76</v>
       </c>
       <c r="J8" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="K8" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="M8" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N8" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="K8" t="s" s="2">
+      <c r="O8" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="L8" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="O8" t="s" s="2">
-        <v>117</v>
       </c>
       <c r="P8" t="s" s="2">
         <v>76</v>
@@ -1778,33 +1766,33 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AK8" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AL8" t="s" s="2">
         <v>118</v>
-      </c>
-      <c r="AG8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI8" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ8" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK8" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AL8" t="s" s="2">
-        <v>121</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1821,102 +1809,102 @@
         <v>76</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="M9" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="N9" t="s" s="2">
         <v>123</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="O9" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="P9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q9" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="N9" t="s" s="2">
+      <c r="R9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X9" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="O9" t="s" s="2">
+      <c r="Y9" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="P9" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q9" t="s" s="2">
+      <c r="Z9" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="R9" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S9" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T9" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U9" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V9" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W9" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X9" t="s" s="2">
+      <c r="AA9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF9" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="Y9" t="s" s="2">
+      <c r="AG9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH9" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ9" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AK9" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="Z9" t="s" s="2">
+      <c r="AL9" t="s" s="2">
         <v>131</v>
-      </c>
-      <c r="AA9" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB9" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AG9" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH9" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI9" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ9" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK9" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AL9" t="s" s="2">
-        <v>134</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1936,22 +1924,22 @@
         <v>76</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="K10" t="s" s="2">
         <v>88</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>76</v>
@@ -2000,7 +1988,7 @@
         <v>76</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -2012,21 +2000,21 @@
         <v>76</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2046,22 +2034,22 @@
         <v>76</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="N11" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="O11" t="s" s="2">
         <v>144</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>147</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>76</v>
@@ -2110,7 +2098,7 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -2119,24 +2107,24 @@
         <v>87</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2156,22 +2144,22 @@
         <v>76</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="L12" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="O12" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>76</v>
@@ -2196,11 +2184,11 @@
         <v>76</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>76</v>
@@ -2218,7 +2206,7 @@
         <v>76</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -2230,21 +2218,21 @@
         <v>76</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2264,16 +2252,16 @@
         <v>76</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2324,33 +2312,33 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AK13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>163</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2453,10 +2441,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2561,10 +2549,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2584,22 +2572,22 @@
         <v>76</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="O16" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>117</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>76</v>
@@ -2648,33 +2636,33 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AK16" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>118</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK16" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>121</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2691,100 +2679,100 @@
         <v>76</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q17" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="R17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="Z17" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="R17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X17" t="s" s="2">
+      <c r="AA17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="Y17" t="s" s="2">
+      <c r="AG17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AK17" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="Z17" t="s" s="2">
+      <c r="AL17" t="s" s="2">
         <v>131</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK17" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>134</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2804,20 +2792,20 @@
         <v>76</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="K18" t="s" s="2">
         <v>88</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>76</v>
@@ -2866,7 +2854,7 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -2878,21 +2866,21 @@
         <v>76</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2912,20 +2900,20 @@
         <v>76</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>76</v>
@@ -2974,7 +2962,7 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -2983,24 +2971,24 @@
         <v>87</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3020,22 +3008,22 @@
         <v>76</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>76</v>
@@ -3060,11 +3048,11 @@
         <v>76</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>76</v>
@@ -3082,7 +3070,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3094,13 +3082,13 @@
         <v>76</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>

--- a/jpcore-r4/main/StructureDefinition-jp-medicationratio-doseperperiod.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationratio-doseperperiod.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/main/StructureDefinition-jp-medicationratio-doseperperiod.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationratio-doseperperiod.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -408,7 +408,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>量を理解し、表現する方法。 / How the Quantity should be understood and represented.</t>
+    <t>数量の評価解釈コード / How the Quantity should be understood and represented.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.0.1</t>
@@ -528,7 +528,7 @@
     <t>Ratio.denominator.comparator</t>
   </si>
   <si>
-    <t>&lt;|&lt;= |&gt; = |&gt;  - 価値を理解する方法 / &lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
+    <t>&lt;|&lt;= |&gt; = |&gt;  - 値の比較方法 / &lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
   </si>
   <si>
     <t>値をどのように理解し、表現する必要があるか - 測定の問題により実際の値が記載されている値よりも大きいか小さいかどうか。例えばコンパレータが「&lt;」の場合、実際の値は&lt;stated値です。 / How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
@@ -904,7 +904,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="70.171875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="66.87109375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="57.89453125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/main/StructureDefinition-jp-medicationratio-doseperperiod.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationratio-doseperperiod.xlsx
@@ -880,43 +880,43 @@
   <dimension ref="A1:AL20"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="29.3828125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="29.3828125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="12.64453125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="25.1875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="25.1875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="72.0078125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="61.734375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="226.484375" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="194.171875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="66.87109375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="57.89453125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="20.22265625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="57.328125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="49.63671875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="17.33984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="28.1484375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="68.94921875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="24.1328125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="59.11328125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/main/StructureDefinition-jp-medicationratio-doseperperiod.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationratio-doseperperiod.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
